--- a/site/exports/ouc-ise-cs.xlsx
+++ b/site/exports/ouc-ise-cs.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R23d4f8eb72904a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rb30f51bd37b44c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R886f14c2632d4162"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc930f3c846ba452b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R11f31afcb6d64527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra1fca786cba14cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R03595a8cf7e5448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R592af41b63b4437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rfe31a53218c943be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Re41182ed27a24d73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T32_0" displayName="T32_0" ref="A1:K3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T34_0" displayName="T34_0" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T32_1" displayName="T32_1" ref="A1:S15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T34_1" displayName="T34_1" ref="A1:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T32_2" displayName="T32_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T34_2" displayName="T34_2" ref="A1:L5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T32_3" displayName="T32_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T34_3" displayName="T34_3" ref="A1:L6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T32_4" displayName="T32_4" ref="A1:G12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T34_4" displayName="T34_4" ref="A1:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -548,10 +548,109 @@
         <x:v>中国海洋大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陈欣</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>信息科学与工程学部·计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>未披露部分不推断，精选论文非全集。；博士院校和其他学历、导师未知；博士后项目主持不等于博士后经历。</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>信息科学与工程学部·计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>未披露部分不推断，精选论文非全集。；加入董军宇团队非导师直接证据，不建师承边。</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str"/>
+      <x:c r="J5" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>信息科学与工程学部·计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>未披露部分不推断，精选论文非全集。；加入郭忠文团队及博士后基金不自动作指导关系或博士后任职。</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str"/>
+      <x:c r="J6" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5741759fa4524fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c9f1180cbf4806"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1268,10 +1367,481 @@
         <x:v>中国海洋大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>陈欣</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str"/>
+      <x:c r="E16" s="6" t="str"/>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str"/>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="str"/>
+      <x:c r="M16" s="7" t="str"/>
+      <x:c r="N16" s="6" t="str"/>
+      <x:c r="O16" s="6" t="str">
+        <x:v>最高学位标签，未给学校、年份及明确获授语句。</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q16" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="R16" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S16" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>陈欣</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>中国海洋大学计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str"/>
+      <x:c r="F17" s="6" t="str"/>
+      <x:c r="G17" s="6" t="str"/>
+      <x:c r="H17" s="6" t="str"/>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str"/>
+      <x:c r="L17" s="6" t="str"/>
+      <x:c r="M17" s="7" t="str"/>
+      <x:c r="N17" s="6" t="str"/>
+      <x:c r="O17" s="6" t="str"/>
+      <x:c r="P17" s="6" t="str"/>
+      <x:c r="Q17" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S17" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>陈欣</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>入职</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str"/>
+      <x:c r="G18" s="6" t="str"/>
+      <x:c r="H18" s="6" t="str"/>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str"/>
+      <x:c r="L18" s="6" t="str"/>
+      <x:c r="M18" s="7" t="str"/>
+      <x:c r="N18" s="6" t="str"/>
+      <x:c r="O18" s="6" t="str">
+        <x:v>入职时间不当讲师晋升日期。</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="str"/>
+      <x:c r="Q18" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J19" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str"/>
+      <x:c r="M19" s="7" t="str"/>
+      <x:c r="N19" s="6" t="str"/>
+      <x:c r="O19" s="6" t="str">
+        <x:v>本科毕业未明确授位。</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q19" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S19" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>香港城市大学</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str">
+        <x:v>中国香港</x:v>
+      </x:c>
+      <x:c r="J20" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str"/>
+      <x:c r="M20" s="7" t="str"/>
+      <x:c r="N20" s="6" t="str"/>
+      <x:c r="O20" s="6" t="str">
+        <x:v>原文硕博就读，未给时间或获授语句。</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q20" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="R20" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>香港城市大学</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I21" s="6" t="str">
+        <x:v>中国香港</x:v>
+      </x:c>
+      <x:c r="J21" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="str"/>
+      <x:c r="M21" s="7" t="str"/>
+      <x:c r="N21" s="6" t="str"/>
+      <x:c r="O21" s="6" t="str">
+        <x:v>原文硕博就读，最高博士标签未给独立获授。</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q21" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S21" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>中国海洋大学计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str"/>
+      <x:c r="L22" s="6" t="str"/>
+      <x:c r="M22" s="7" t="str"/>
+      <x:c r="N22" s="6" t="str"/>
+      <x:c r="O22" s="6" t="str"/>
+      <x:c r="P22" s="6" t="str"/>
+      <x:c r="Q22" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="R22" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S22" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>入职</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>2022-10</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str"/>
+      <x:c r="L23" s="6" t="str"/>
+      <x:c r="M23" s="7" t="str"/>
+      <x:c r="N23" s="6" t="str"/>
+      <x:c r="O23" s="6" t="str">
+        <x:v>不当职称起始。</x:v>
+      </x:c>
+      <x:c r="P23" s="6" t="str"/>
+      <x:c r="Q23" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="R23" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S23" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>山东大学</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str">
+        <x:v>2019-06</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>工学</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="str"/>
+      <x:c r="M24" s="7" t="str"/>
+      <x:c r="N24" s="6" t="str"/>
+      <x:c r="O24" s="6" t="str">
+        <x:v>仅工学学士标签，不由博士已获授推本科授位。</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q24" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="R24" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S24" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>山东大学</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str">
+        <x:v>2024-06</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>工学</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L25" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="str"/>
+      <x:c r="N25" s="6" t="str"/>
+      <x:c r="O25" s="6" t="str">
+        <x:v>简介明确2024.06获得工学博士。</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q25" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="R25" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S25" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>中国海洋大学计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>2024-08</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str"/>
+      <x:c r="G26" s="6" t="str"/>
+      <x:c r="H26" s="6" t="str"/>
+      <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str"/>
+      <x:c r="K26" s="6" t="str"/>
+      <x:c r="L26" s="6" t="str"/>
+      <x:c r="M26" s="7" t="str"/>
+      <x:c r="N26" s="6" t="str"/>
+      <x:c r="O26" s="6" t="str">
+        <x:v>教育工作经历明确起职。</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="str"/>
+      <x:c r="Q26" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="R26" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="S26" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35701ed05af841c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R957def38a898400a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1404,10 +1974,86 @@
         <x:v>中国海洋大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Sam Kwong</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>硕博合述导师（未拆分阶段）</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>硕博合述，具体分别阶段未拆证</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>本人硕博合述导师；岭南官网列协理副校长（策略研究）及计算智能讲座教授。</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>岭南本人现职页直接列示，不作人事核验。；合述仅计一条关系，不拆分阶段导师认定；combined_masters_doctoral_statement_not_separate_edges；关联经历ID：["ouc-caojingchao-education-2", "ouc-caojingchao-education-3"]；合述机构未单独披露；指导起止：起始时间未披露 至 结束时间未披露</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://www.ln.edu.hk/po/people/professor-sam-kwong-tak-wu</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>https://www.ln.edu.hk/po/people/professor-sam-kwong-tak-wu</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>于东晓</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>本人明确博士导师；山东大学官网列教授，研究边缘智能与分布式计算。</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>官方现行个人页与教授名录列示；不推人事全职。</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>https://www.cs.sdu.edu.cn/info/1070/5367.htm</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>https://www.cs.sdu.edu.cn/info/1070/5367.htm</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra50fe888360e404b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5092e57f5a843e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1540,10 +2186,118 @@
         <x:v>中国海洋大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陈欣</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Bounding quality of pure Nash equilibria in dual-role facility location games</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str"/>
+      <x:c r="E4" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>官网精选列表，未逐篇出版者核。</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>ERD: Encoder-Residual-Decoder Neural Network for Underwater Image Enhancement</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str"/>
+      <x:c r="E5" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>本人官网第一项，未逐篇出版者核。</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Privacy-enhanced Decentralized Federated Learning at Dynamic Edge</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str"/>
+      <x:c r="E6" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>本人官网列表，未逐篇出版者核。</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra067f73d0fad48f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97397493edc74c28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1793,16 +2547,16 @@
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
-        <x:v>张巍</x:v>
+        <x:v>陈欣</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>chenxin-source-1</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://it.ouc.edu.cn/21691/list.htm</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
       </x:c>
       <x:c r="E11" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1816,16 +2570,16 @@
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
-        <x:v>曹媛</x:v>
+        <x:v>陈欣</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>institution-classification-6</x:v>
+        <x:v>chenxin-source-2</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://it.ouc.edu.cn/cx/list.htm</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
       </x:c>
       <x:c r="E12" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1834,13 +2588,243 @@
         <x:v>ouc</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>caojingchao-source-1</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/21691/list.htm</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>caojingchao-source-2</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/cjc/list.htm</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>caojingchao-source-3</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>https://www.ln.edu.hk/po/people/professor-sam-kwong-tak-wu</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>已审官方机构或出版元数据，仅覆盖所列结构字段。；official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>chenshuzhen-source-1</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/21691/list.htm</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>chenshuzhen-source-2</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>https://it.ouc.edu.cn/zcs/list.htm</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>chenshuzhen-source-3</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>https://www.cs.sdu.edu.cn/info/1070/5367.htm</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>已审官方机构或出版元数据，仅覆盖所列结构字段。；official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>张巍</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>曹媛</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>曹景超</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>中国海洋大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>陈姝祯</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>ouc</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
         <x:v>中国海洋大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa9fb14fbf3d4898"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f554c59cece42a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/ouc-ise-cs.xlsx
+++ b/site/exports/ouc-ise-cs.xlsx
@@ -452,8 +452,8 @@
     <col width="47.59999999999999" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
